--- a/artfynd/S 1111-2025 artfynd.xlsx
+++ b/artfynd/S 1111-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY169"/>
+  <dimension ref="A1:AZ169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102578298</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583828</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102573216</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583859</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583860</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583861</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597213</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1495,6 +1535,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627569</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1611,6 +1656,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627571</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1727,6 +1777,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627574</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1843,6 +1898,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627575</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1959,6 +2019,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627588</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2075,6 +2140,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627607</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2191,6 +2261,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627611</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2292,6 +2367,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583827</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2408,6 +2488,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627593</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2509,6 +2594,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583841</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2625,6 +2715,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627613</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2741,6 +2836,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627617</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2855,6 +2955,11 @@
       <c r="AY21" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627598</t>
         </is>
       </c>
     </row>
@@ -2962,6 +3067,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102578254</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3063,6 +3173,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627585</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3164,6 +3279,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627577</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3261,6 +3381,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102573190</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3366,6 +3491,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102578148</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3471,6 +3601,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102578160</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3587,6 +3722,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627573</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3703,6 +3843,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627581</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3820,6 +3965,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627612</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3922,6 +4072,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102573213</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4019,6 +4174,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102573214</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4116,6 +4276,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102573215</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4217,6 +4382,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583854</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4318,6 +4488,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583855</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4419,6 +4594,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583856</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4520,6 +4700,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583858</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4621,6 +4806,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597256</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4722,6 +4912,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597257</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4823,6 +5018,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597258</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4924,6 +5124,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597259</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5040,6 +5245,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627578</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5156,6 +5366,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627604</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5272,6 +5487,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627605</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5388,6 +5608,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627610</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5504,6 +5729,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627618</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5605,6 +5835,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583863</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5706,6 +5941,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583864</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5803,6 +6043,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102573200</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5900,6 +6145,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102573202</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5997,6 +6247,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102573203</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6094,6 +6349,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102573205</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6191,6 +6451,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102573206</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6288,6 +6553,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102573207</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6385,6 +6655,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102573208</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6486,6 +6761,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583852</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6587,6 +6867,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597214</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6688,6 +6973,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597216</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6789,6 +7079,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597218</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6890,6 +7185,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597220</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6991,6 +7291,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597222</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7092,6 +7397,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597224</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7193,6 +7503,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597227</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7294,6 +7609,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597229</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7395,6 +7715,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597232</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7496,6 +7821,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597235</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7597,6 +7927,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597247</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7698,6 +8033,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597248</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7799,6 +8139,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597249</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7900,6 +8245,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597250</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8001,6 +8351,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597251</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8102,6 +8457,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597252</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8203,6 +8563,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597253</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8304,6 +8669,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597255</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8420,6 +8790,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627579</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8536,6 +8911,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627606</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8652,6 +9032,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627608</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8749,6 +9134,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102573183</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8850,6 +9240,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583816</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8951,6 +9346,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583817</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9052,6 +9452,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583818</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9153,6 +9558,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583819</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9254,6 +9664,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583821</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9355,6 +9770,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583822</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9456,6 +9876,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583823</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9557,6 +9982,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583825</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9658,6 +10088,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597206</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9759,6 +10194,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597207</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9861,6 +10301,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597208</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9962,6 +10407,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597212</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10059,6 +10509,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102573186</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10164,6 +10619,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102578239</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10265,6 +10725,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583835</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10366,6 +10831,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583836</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10467,6 +10937,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583837</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10568,6 +11043,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583839</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10669,6 +11149,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583840</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10785,6 +11270,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627572</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10901,6 +11391,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627587</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11017,6 +11512,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627594</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11133,6 +11633,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627601</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11249,6 +11754,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627602</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11357,6 +11867,11 @@
       <c r="AY103" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17277432</t>
         </is>
       </c>
     </row>
@@ -11464,6 +11979,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102578272</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11569,6 +12089,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102578329</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11674,6 +12199,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102578342</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11775,6 +12305,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583851</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11876,6 +12411,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597246</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11992,6 +12532,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627589</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12108,6 +12653,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627597</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12224,6 +12774,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627596</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12325,6 +12880,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583862</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12441,6 +13001,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627595</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12555,6 +13120,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583829</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12664,6 +13234,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583830</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12769,6 +13344,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583831</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12866,6 +13446,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102573209</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12963,6 +13548,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102573210</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13060,6 +13650,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102573211</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13161,6 +13756,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583853</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13262,6 +13862,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627570</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13363,6 +13968,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627609</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13473,6 +14083,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17277481</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13570,6 +14185,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102573191</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13667,6 +14287,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102573188</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13768,6 +14393,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583833</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13865,6 +14495,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102573193</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13962,6 +14597,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102573194</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14067,6 +14707,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102578180</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14172,6 +14817,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102578260</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14273,6 +14923,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583843</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14374,6 +15029,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583844</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14475,6 +15135,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583845</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14576,6 +15241,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583847</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14677,6 +15347,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583848</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14778,6 +15453,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583849</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14879,6 +15559,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583850</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14980,6 +15665,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597215</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15081,6 +15771,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597217</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15182,6 +15877,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597219</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15283,6 +15983,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597221</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15384,6 +16089,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597223</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15485,6 +16195,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597226</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15586,6 +16301,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597228</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15687,6 +16407,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597230</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15788,6 +16513,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597233</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15889,6 +16619,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597234</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15990,6 +16725,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597236</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16091,6 +16831,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597237</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16192,6 +16937,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597238</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16293,6 +17043,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597239</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16394,6 +17149,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597240</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16495,6 +17255,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597241</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16596,6 +17361,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597242</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16697,6 +17467,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597243</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16798,6 +17573,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597244</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16899,6 +17679,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597245</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17015,6 +17800,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627580</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17131,6 +17921,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627590</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17247,6 +18042,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627600</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17363,6 +18163,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627615</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -17460,6 +18265,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102573185</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17561,6 +18371,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102583826</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -17662,6 +18477,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597209</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17763,6 +18583,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597210</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17864,6 +18689,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102597211</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17980,6 +18810,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627586</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -18096,6 +18931,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627591</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18212,8 +19052,183 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627599</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>